--- a/target/classes/com/mycompany/ocxrst/BASES/PRODUCTOPROVEEDORES.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PRODUCTOPROVEEDORES.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
   <si>
     <t>CODIGO_PRODUCTO</t>
   </si>
@@ -60,6 +60,18 @@
   </si>
   <si>
     <t>lala08</t>
+  </si>
+  <si>
+    <t>prue01</t>
+  </si>
+  <si>
+    <t>QWEQ</t>
+  </si>
+  <si>
+    <t>2050</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -104,7 +116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -144,7 +156,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -164,6 +176,26 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
     </row>
